--- a/Mica/Taxonomy_example.xlsx
+++ b/Mica/Taxonomy_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Working projects\ADM\R-Packages\C_OpalLUMCADM\Mica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12711E57-BEDF-498A-A553-A1B29996F630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C7B7A8-79C8-4FD6-8928-FFBA1977157D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A2D679C-4E0B-498D-ACF8-23C3F7F9D733}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{8A2D679C-4E0B-498D-ACF8-23C3F7F9D733}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="82">
   <si>
     <t>vocabulary</t>
   </si>
@@ -256,9 +256,6 @@
     <t>All biomarkers</t>
   </si>
   <si>
-    <t>Biomarker_A</t>
-  </si>
-  <si>
     <t>Id of the taxonomy</t>
   </si>
   <si>
@@ -281,6 +278,12 @@
   </si>
   <si>
     <t xml:space="preserve">Fill in both tabs </t>
+  </si>
+  <si>
+    <t>Var1</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -346,6 +349,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>335288</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>182887</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C39D6D6E-0FDE-C03C-406C-D40DADA018B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8001000" y="762000"/>
+          <a:ext cx="3992888" cy="3230887"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -666,44 +724,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2DF075-1ABA-425C-B2E8-5F4BD7BF414A}">
   <dimension ref="A2:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="28.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -711,13 +769,13 @@
         <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -725,27 +783,27 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -753,13 +811,13 @@
         <v>61</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -767,27 +825,27 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -795,13 +853,13 @@
         <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -809,98 +867,99 @@
         <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873FD838-5310-423D-9070-1307AC7B2FD7}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" customWidth="1"/>
+    <col min="1" max="9" width="21.453125" customWidth="1"/>
+    <col min="10" max="10" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -929,7 +988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -958,7 +1017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -987,7 +1046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1016,7 +1075,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -1045,7 +1104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -1074,7 +1133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -1103,7 +1162,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1132,7 +1191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1169,12 +1228,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52E92C84-4FB4-45ED-A47A-70BA56F29B32}">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="17.85546875" customWidth="1"/>
+    <col min="1" max="4" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -1188,7 +1247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1202,7 +1261,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -1216,7 +1275,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1230,7 +1289,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1244,7 +1303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1258,7 +1317,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1272,7 +1331,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1286,7 +1345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1300,7 +1359,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1314,7 +1373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1328,7 +1387,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1342,7 +1401,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1356,7 +1415,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1370,7 +1429,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1384,7 +1443,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1398,7 +1457,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -1412,7 +1471,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1426,7 +1485,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1440,7 +1499,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1454,7 +1513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1468,7 +1527,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -1482,7 +1541,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -1496,7 +1555,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -1510,7 +1569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1524,7 +1583,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1538,7 +1597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -1552,7 +1611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1566,7 +1625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -1580,7 +1639,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -1594,7 +1653,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -1608,7 +1667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -1622,7 +1681,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -1636,7 +1695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>49</v>
       </c>
@@ -1650,7 +1709,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -1664,7 +1723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1678,7 +1737,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -1692,7 +1751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -1706,7 +1765,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -1720,7 +1779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -1734,7 +1793,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -1748,7 +1807,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -1762,7 +1821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -1776,7 +1835,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -1790,7 +1849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>54</v>
       </c>
@@ -1804,7 +1863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -1818,7 +1877,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -1832,7 +1891,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -1846,7 +1905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1860,7 +1919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1874,7 +1933,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -1888,7 +1947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -1902,7 +1961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -1916,7 +1975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>57</v>
       </c>

--- a/Mica/Taxonomy_example.xlsx
+++ b/Mica/Taxonomy_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Working projects\ADM\R-Packages\C_OpalLUMCADM\Mica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C7B7A8-79C8-4FD6-8928-FFBA1977157D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE41727-7305-40BD-B339-0B080E337647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{8A2D679C-4E0B-498D-ACF8-23C3F7F9D733}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A2D679C-4E0B-498D-ACF8-23C3F7F9D733}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="85">
   <si>
     <t>vocabulary</t>
   </si>
@@ -284,13 +284,22 @@
   </si>
   <si>
     <t>l</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>url_link</t>
+  </si>
+  <si>
+    <t>url_type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,6 +314,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -327,13 +342,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -724,17 +740,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2DF075-1ABA-425C-B2E8-5F4BD7BF414A}">
   <dimension ref="A2:G25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.54296875" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>76</v>
       </c>
@@ -742,12 +758,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -761,7 +777,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -775,7 +791,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -789,7 +805,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -803,7 +819,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -817,7 +833,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -831,7 +847,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -845,7 +861,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -859,7 +875,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -873,12 +889,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -892,7 +908,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -906,7 +922,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -920,7 +936,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -934,12 +950,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>75</v>
       </c>
@@ -953,13 +969,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873FD838-5310-423D-9070-1307AC7B2FD7}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="9" width="21.453125" customWidth="1"/>
-    <col min="10" max="10" width="21.54296875" customWidth="1"/>
+    <col min="1" max="9" width="21.42578125" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -988,7 +1004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1017,7 +1033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1046,7 +1062,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1075,7 +1091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -1104,7 +1120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -1133,7 +1149,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -1162,7 +1178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1191,7 +1207,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1227,13 +1243,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52E92C84-4FB4-45ED-A47A-70BA56F29B32}">
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="17.81640625" customWidth="1"/>
+    <col min="1" max="4" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -1247,9 +1263,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -1261,23 +1277,23 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -1289,23 +1305,23 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>37</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -1317,9 +1333,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -1328,10 +1344,10 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1339,41 +1355,41 @@
         <v>58</v>
       </c>
       <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1381,43 +1397,43 @@
         <v>58</v>
       </c>
       <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
@@ -1429,9 +1445,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -1443,7 +1459,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1451,41 +1467,41 @@
         <v>58</v>
       </c>
       <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
         <v>12</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1493,43 +1509,43 @@
         <v>58</v>
       </c>
       <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>58</v>
@@ -1541,23 +1557,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>45</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
@@ -1569,9 +1585,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
         <v>58</v>
@@ -1583,9 +1599,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
         <v>58</v>
@@ -1597,9 +1613,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
         <v>58</v>
@@ -1611,9 +1627,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
         <v>58</v>
@@ -1625,9 +1641,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
         <v>58</v>
@@ -1636,10 +1652,10 @@
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -1647,43 +1663,43 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" t="s">
         <v>12</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D32" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>48</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -1695,9 +1711,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
         <v>58</v>
@@ -1709,9 +1725,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
         <v>58</v>
@@ -1720,12 +1736,12 @@
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
         <v>58</v>
@@ -1737,9 +1753,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
         <v>58</v>
@@ -1751,23 +1767,23 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>51</v>
-      </c>
-      <c r="B38" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>52</v>
       </c>
       <c r="B39" t="s">
         <v>58</v>
@@ -1779,9 +1795,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
@@ -1790,10 +1806,10 @@
         <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -1801,41 +1817,41 @@
         <v>58</v>
       </c>
       <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
         <v>12</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -1843,43 +1859,43 @@
         <v>58</v>
       </c>
       <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
         <v>12</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>54</v>
-      </c>
-      <c r="B45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>55</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
@@ -1891,23 +1907,23 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>55</v>
-      </c>
-      <c r="B48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>56</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
@@ -1919,9 +1935,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
         <v>58</v>
@@ -1930,10 +1946,10 @@
         <v>22</v>
       </c>
       <c r="D50" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -1941,41 +1957,41 @@
         <v>58</v>
       </c>
       <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
         <v>12</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D53" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" t="s">
-        <v>58</v>
-      </c>
-      <c r="C52" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -1983,10 +1999,94 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" t="s">
         <v>12</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D56" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
